--- a/docs/validation/V08_Cases_vs_Dollars_Separation.xlsx
+++ b/docs/validation/V08_Cases_vs_Dollars_Separation.xlsx
@@ -677,7 +677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F143"/>
+  <dimension ref="A1:F155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -837,7 +837,7 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>45 minutes across all three reports.</t>
+          <t>60 minutes across all three reports.</t>
         </is>
       </c>
       <c r="D14" s="7" t="n"/>
@@ -1247,7 +1247,7 @@
       <c r="E51" s="7" t="n"/>
       <c r="F51" s="8" t="n"/>
     </row>
-    <row r="52" ht="28" customHeight="1">
+    <row r="52" ht="29.5" customHeight="1">
       <c r="B52" s="12" t="inlineStr">
         <is>
           <t>The one permitted pairing</t>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>Total Cases YoY % with National Liquor Stores Real YoY % — visual 3.5 only</t>
+          <t>Total Cases YoY % with National Liquor Stores Real YoY % — side by side in 3.5, and as a difference in Volume Gap vs National (pp) on 3.3 and 3.6</t>
         </is>
       </c>
       <c r="D52" s="7" t="n"/>
@@ -1395,278 +1395,278 @@
       </c>
       <c r="F62" s="18" t="inlineStr"/>
     </row>
-    <row r="63" ht="42" customHeight="1">
-      <c r="B63" s="12" t="inlineStr">
+    <row r="63" ht="43" customHeight="1">
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>R1 P3</t>
         </is>
       </c>
-      <c r="C63" s="12" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>On-Premise Share KPI</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>Share of cases, reference vs 2019 in pp — no dollar measure in any well or tooltip</t>
+        </is>
+      </c>
+      <c r="F63" s="18" t="n"/>
+    </row>
+    <row r="64" ht="83.5" customHeight="1">
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>R1 P3</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>Volume Gap KPI</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>Volume Gap vs National (pp) is local case growth against national growth. Open the measure (document 20) and confirm its national leg is National Liquor Stores Real YoY %, never the nominal series</t>
+        </is>
+      </c>
+      <c r="F64" s="18" t="n"/>
+    </row>
+    <row r="65" ht="43" customHeight="1">
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>R1 P3</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>Volume Gap by Class</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>Same measure as 3.3 — real national leg only; axis titled as case growth, not sales</t>
+        </is>
+      </c>
+      <c r="F65" s="18" t="n"/>
+    </row>
+    <row r="66" ht="42" customHeight="1">
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>R1 P3</t>
+        </is>
+      </c>
+      <c r="C66" s="12" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="D63" s="12" t="inlineStr">
+      <c r="D66" s="12" t="inlineStr">
         <is>
           <t>Local Volume vs National Real</t>
         </is>
       </c>
-      <c r="E63" s="12" t="inlineStr">
+      <c r="E66" s="12" t="inlineStr">
         <is>
           <t>The permitted pairing — the national line must be the Real YoY %, never nominal</t>
         </is>
       </c>
-      <c r="F63" s="19" t="inlineStr"/>
-    </row>
-    <row r="64" ht="28" customHeight="1">
-      <c r="B64" s="10" t="inlineStr">
+      <c r="F66" s="19" t="inlineStr"/>
+    </row>
+    <row r="67" ht="28" customHeight="1">
+      <c r="B67" s="10" t="inlineStr">
         <is>
           <t>R1 P3</t>
         </is>
       </c>
-      <c r="C64" s="10" t="inlineStr">
+      <c r="C67" s="10" t="inlineStr">
         <is>
           <t>3.7</t>
         </is>
       </c>
-      <c r="D64" s="10" t="inlineStr">
+      <c r="D67" s="10" t="inlineStr">
         <is>
           <t>Supplier and Item Detail</t>
         </is>
       </c>
-      <c r="E64" s="10" t="inlineStr">
+      <c r="E67" s="10" t="inlineStr">
         <is>
           <t>Matrix: case values only; no dollar column</t>
         </is>
       </c>
-      <c r="F64" s="18" t="inlineStr"/>
-    </row>
-    <row r="65" ht="16" customHeight="1">
-      <c r="B65" s="12" t="inlineStr">
+      <c r="F67" s="18" t="inlineStr"/>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="B68" s="12" t="inlineStr">
         <is>
           <t>R1 P3</t>
         </is>
       </c>
-      <c r="C65" s="12" t="inlineStr">
+      <c r="C68" s="12" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
       </c>
-      <c r="D65" s="12" t="inlineStr">
+      <c r="D68" s="12" t="inlineStr">
         <is>
           <t>Channel split</t>
         </is>
       </c>
-      <c r="E65" s="12" t="inlineStr">
+      <c r="E68" s="12" t="inlineStr">
         <is>
           <t>Axis titled Cases</t>
         </is>
       </c>
-      <c r="F65" s="19" t="inlineStr"/>
-    </row>
-    <row r="66" ht="28" customHeight="1">
-      <c r="B66" s="10" t="inlineStr">
+      <c r="F68" s="19" t="inlineStr"/>
+    </row>
+    <row r="69" ht="29.5" customHeight="1">
+      <c r="B69" s="12" t="inlineStr">
         <is>
           <t>R1 P3</t>
         </is>
       </c>
-      <c r="C66" s="10" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D66" s="10" t="inlineStr">
-        <is>
-          <t>Narrative on Page 3</t>
-        </is>
-      </c>
-      <c r="E66" s="10" t="inlineStr">
-        <is>
-          <t>No sentence compares cases with dollars</t>
-        </is>
-      </c>
-      <c r="F66" s="18" t="inlineStr"/>
-    </row>
-    <row r="67" ht="28" customHeight="1">
-      <c r="B67" s="12" t="inlineStr">
-        <is>
-          <t>R2 P1</t>
-        </is>
-      </c>
-      <c r="C67" s="12" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="D67" s="12" t="inlineStr">
-        <is>
-          <t>Stress vs Volume</t>
-        </is>
-      </c>
-      <c r="E67" s="12" t="inlineStr">
-        <is>
-          <t>Column axis labelled as case growth, not sales</t>
-        </is>
-      </c>
-      <c r="F67" s="19" t="inlineStr"/>
-    </row>
-    <row r="68" ht="28" customHeight="1">
-      <c r="B68" s="10" t="inlineStr">
-        <is>
-          <t>R2 P1</t>
-        </is>
-      </c>
-      <c r="C68" s="10" t="inlineStr">
-        <is>
-          <t>4.6a–d</t>
-        </is>
-      </c>
-      <c r="D68" s="10" t="inlineStr">
-        <is>
-          <t>Four item-type scatters</t>
-        </is>
-      </c>
-      <c r="E68" s="10" t="inlineStr">
-        <is>
-          <t>Y axis is Total Cases YoY %; no dollar measure in any well</t>
-        </is>
-      </c>
-      <c r="F68" s="18" t="inlineStr"/>
-    </row>
-    <row r="69" ht="28" customHeight="1">
-      <c r="B69" s="12" t="inlineStr">
-        <is>
-          <t>R2 P1</t>
-        </is>
-      </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>3.10, 3.11</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Income Channel</t>
+          <t>On-premise share vs 2019; Keg share</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Total Cases YoY % beside income growth — no dollar sales</t>
-        </is>
-      </c>
-      <c r="F69" s="19" t="inlineStr"/>
+          <t>Shares of cases only; no dollar series in any well or tooltip</t>
+        </is>
+      </c>
+      <c r="F69" s="19" t="n"/>
     </row>
     <row r="70" ht="28" customHeight="1">
       <c r="B70" s="10" t="inlineStr">
         <is>
+          <t>R1 P3</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>Narrative on Page 3</t>
+        </is>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>No sentence compares cases with dollars</t>
+        </is>
+      </c>
+      <c r="F70" s="18" t="inlineStr"/>
+    </row>
+    <row r="71" ht="28" customHeight="1">
+      <c r="B71" s="12" t="inlineStr">
+        <is>
           <t>R2 P1</t>
         </is>
       </c>
-      <c r="C70" s="10" t="inlineStr">
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>Stress vs Volume</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t>Column axis labelled as case growth, not sales</t>
+        </is>
+      </c>
+      <c r="F71" s="19" t="inlineStr"/>
+    </row>
+    <row r="72" ht="28" customHeight="1">
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>R2 P1</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>4.6a–d</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>Four item-type scatters</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>Y axis is Total Cases YoY %; no dollar measure in any well</t>
+        </is>
+      </c>
+      <c r="F72" s="18" t="inlineStr"/>
+    </row>
+    <row r="73" ht="28" customHeight="1">
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>R2 P1</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>Income Channel</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>Total Cases YoY % beside income growth — no dollar sales</t>
+        </is>
+      </c>
+      <c r="F73" s="19" t="inlineStr"/>
+    </row>
+    <row r="74" ht="28" customHeight="1">
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>R2 P1</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
         <is>
           <t>4.9</t>
         </is>
       </c>
-      <c r="D70" s="10" t="inlineStr">
+      <c r="D74" s="10" t="inlineStr">
         <is>
           <t>Findings text box</t>
         </is>
       </c>
-      <c r="E70" s="10" t="inlineStr">
+      <c r="E74" s="10" t="inlineStr">
         <is>
           <t>No sentence compares cases with dollars</t>
-        </is>
-      </c>
-      <c r="F70" s="18" t="inlineStr"/>
-    </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="B71" s="12" t="inlineStr">
-        <is>
-          <t>R2 P2</t>
-        </is>
-      </c>
-      <c r="C71" s="12" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="D71" s="12" t="inlineStr">
-        <is>
-          <t>Total Cases YoY KPI</t>
-        </is>
-      </c>
-      <c r="E71" s="12" t="inlineStr">
-        <is>
-          <t>Case measure only</t>
-        </is>
-      </c>
-      <c r="F71" s="19" t="inlineStr"/>
-    </row>
-    <row r="72" ht="16" customHeight="1">
-      <c r="B72" s="10" t="inlineStr">
-        <is>
-          <t>R2 P2</t>
-        </is>
-      </c>
-      <c r="C72" s="10" t="inlineStr">
-        <is>
-          <t>5.8</t>
-        </is>
-      </c>
-      <c r="D72" s="10" t="inlineStr">
-        <is>
-          <t>Mix Detail</t>
-        </is>
-      </c>
-      <c r="E72" s="10" t="inlineStr">
-        <is>
-          <t>Matrix: case values only</t>
-        </is>
-      </c>
-      <c r="F72" s="18" t="inlineStr"/>
-    </row>
-    <row r="73" ht="16" customHeight="1">
-      <c r="B73" s="12" t="inlineStr">
-        <is>
-          <t>R3 P1</t>
-        </is>
-      </c>
-      <c r="C73" s="12" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="D73" s="12" t="inlineStr">
-        <is>
-          <t>Pareto</t>
-        </is>
-      </c>
-      <c r="E73" s="12" t="inlineStr">
-        <is>
-          <t>Column axis titled Cases</t>
-        </is>
-      </c>
-      <c r="F73" s="19" t="inlineStr"/>
-    </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="B74" s="10" t="inlineStr">
-        <is>
-          <t>R3 P3</t>
-        </is>
-      </c>
-      <c r="C74" s="10" t="inlineStr">
-        <is>
-          <t>9.7</t>
-        </is>
-      </c>
-      <c r="D74" s="10" t="inlineStr">
-        <is>
-          <t>Distribution Quality</t>
-        </is>
-      </c>
-      <c r="E74" s="10" t="inlineStr">
-        <is>
-          <t>X axis titled Cases</t>
         </is>
       </c>
       <c r="F74" s="18" t="inlineStr"/>
@@ -1674,22 +1674,22 @@
     <row r="75" ht="16" customHeight="1">
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>R3 P3</t>
+          <t>R2 P2</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Supplier Detail</t>
+          <t>Total Cases YoY KPI</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Matrix: case values only</t>
+          <t>Case measure only</t>
         </is>
       </c>
       <c r="F75" s="19" t="inlineStr"/>
@@ -1697,706 +1697,982 @@
     <row r="76" ht="16" customHeight="1">
       <c r="B76" s="10" t="inlineStr">
         <is>
+          <t>R2 P2</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>Mix Detail</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>Matrix: case values only</t>
+        </is>
+      </c>
+      <c r="F76" s="18" t="inlineStr"/>
+    </row>
+    <row r="77" ht="43" customHeight="1">
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>R2 P2</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>5.3–5.7</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>Keg Share Shift, Mix Shift Magnitude, Mix Composition, Mix Shift vs 2019, Mix Shift vs Stress</t>
+        </is>
+      </c>
+      <c r="E77" s="10" t="inlineStr">
+        <is>
+          <t>Shares of cases and the stress index only — no dollar measure in any well or tooltip</t>
+        </is>
+      </c>
+      <c r="F77" s="18" t="n"/>
+    </row>
+    <row r="78" ht="16" customHeight="1">
+      <c r="B78" s="12" t="inlineStr">
+        <is>
+          <t>R3 P1</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>Pareto</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="inlineStr">
+        <is>
+          <t>Column axis titled Cases</t>
+        </is>
+      </c>
+      <c r="F78" s="19" t="inlineStr"/>
+    </row>
+    <row r="79" ht="43" customHeight="1">
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>R3 P1</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>7.1–7.4, 7.6–7.8</t>
+        </is>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>KPI row, Concentration Over Time, Assortment Churn, Concentration by Type</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>Item counts and cases only — R3 is Tier 3 only (document 15 §7)</t>
+        </is>
+      </c>
+      <c r="F79" s="19" t="n"/>
+    </row>
+    <row r="80" ht="29.5" customHeight="1">
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>R3 P2</t>
+        </is>
+      </c>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>8.2–8.8</t>
+        </is>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>Cohort and survival visuals</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="inlineStr">
+        <is>
+          <t>Item counts and survival rates only; no dollar measure</t>
+        </is>
+      </c>
+      <c r="F80" s="19" t="n"/>
+    </row>
+    <row r="81" ht="16" customHeight="1">
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>R3 P3</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>9.7</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>Distribution Quality</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>X axis titled Cases</t>
+        </is>
+      </c>
+      <c r="F81" s="18" t="inlineStr"/>
+    </row>
+    <row r="82" ht="16" customHeight="1">
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>R3 P3</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>9.8</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>Supplier Detail</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="inlineStr">
+        <is>
+          <t>Matrix: case values only</t>
+        </is>
+      </c>
+      <c r="F82" s="19" t="inlineStr"/>
+    </row>
+    <row r="83" ht="29.5" customHeight="1">
+      <c r="B83" s="12" t="inlineStr">
+        <is>
+          <t>R3 P3</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>9.1–9.6</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>KPI row, Concentration Trend, Share vs Count</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
+        <is>
+          <t>Shares of cases, counts and HHI only; no dollar measure</t>
+        </is>
+      </c>
+      <c r="F83" s="19" t="n"/>
+    </row>
+    <row r="84" ht="16" customHeight="1">
+      <c r="B84" s="10" t="inlineStr">
+        <is>
           <t>R3 P4</t>
         </is>
       </c>
-      <c r="C76" s="10" t="inlineStr">
+      <c r="C84" s="10" t="inlineStr">
         <is>
           <t>10.5</t>
         </is>
       </c>
-      <c r="D76" s="10" t="inlineStr">
+      <c r="D84" s="10" t="inlineStr">
         <is>
           <t>Adjusted vs Raw</t>
         </is>
       </c>
-      <c r="E76" s="10" t="inlineStr">
+      <c r="E84" s="10" t="inlineStr">
         <is>
           <t>Axis titled Cases</t>
         </is>
       </c>
-      <c r="F76" s="18" t="inlineStr"/>
-    </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="B77" s="20" t="inlineStr">
-        <is>
-          <t>Every visual in document 15 that carries a case measure, plus the text on the same pages.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="8" customHeight="1"/>
-    <row r="79" ht="22" customHeight="1">
-      <c r="A79" s="5" t="inlineStr">
+      <c r="F84" s="18" t="inlineStr"/>
+    </row>
+    <row r="85" ht="56.5" customHeight="1">
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>R3 P4</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>10.1–10.4, 10.6–10.8</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>Seasonality KPIs, profiles, method note</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>Case-based factors only; the method note names Census X-13 as a method, not as a comparison of values</t>
+        </is>
+      </c>
+      <c r="F85" s="18" t="n"/>
+    </row>
+    <row r="86" ht="29.5" customHeight="1">
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>Item Detail</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>Drillthrough page (document 15 §8.3)</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>Matrix and line in cases only</t>
+        </is>
+      </c>
+      <c r="F86" s="18" t="n"/>
+    </row>
+    <row r="87" ht="43" customHeight="1">
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>Tooltip page</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>Report tooltip page (document 15 §8.4)</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>Case sparkline and ratio — list the visuals that use it; none may be a dollar visual</t>
+        </is>
+      </c>
+      <c r="F87" s="18" t="n"/>
+    </row>
+    <row r="88" ht="29.5" customHeight="1">
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>Narratives on R1 Pages 1–2 (1.8) and R3 (10.8)</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>No sentence compares cases with dollars</t>
+        </is>
+      </c>
+      <c r="F88" s="18" t="n"/>
+    </row>
+    <row r="89" ht="16" customHeight="1">
+      <c r="B89" s="20" t="inlineStr">
+        <is>
+          <t>Every visual in document 15 that carries a case measure, the text on those pages, the drillthrough page and the tooltip page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="8" customHeight="1"/>
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
         <is>
           <t>5. DECIDE: PASS OR FAIL</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="16" customHeight="1">
-      <c r="B80" s="14" t="inlineStr">
+    <row r="92" ht="16" customHeight="1">
+      <c r="B92" s="14" t="inlineStr">
         <is>
           <t>Decide against the pass criterion only — it is repeated in At a Glance. Find the row below that matches what you saw.</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="B81" s="6" t="inlineStr">
+    <row r="93" ht="20" customHeight="1">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>If you see</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t>It means</t>
         </is>
       </c>
-      <c r="D81" s="8" t="n"/>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="D93" s="8" t="n"/>
+      <c r="E93" s="6" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="F81" s="8" t="n"/>
-    </row>
-    <row r="82" ht="16" customHeight="1">
-      <c r="B82" s="10" t="inlineStr">
+      <c r="F93" s="8" t="n"/>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="B94" s="10" t="inlineStr">
         <is>
           <t>Every row Pass</t>
         </is>
       </c>
-      <c r="C82" s="10" t="inlineStr">
+      <c r="C94" s="10" t="inlineStr">
         <is>
           <t>Cases and dollars never meet except in 3.5, as real growth rates</t>
         </is>
       </c>
-      <c r="D82" s="8" t="n"/>
-      <c r="E82" s="10" t="inlineStr">
+      <c r="D94" s="8" t="n"/>
+      <c r="E94" s="10" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="F82" s="8" t="n"/>
-    </row>
-    <row r="83" ht="16" customHeight="1">
-      <c r="B83" s="12" t="inlineStr">
+      <c r="F94" s="8" t="n"/>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="B95" s="12" t="inlineStr">
         <is>
           <t>Any row fails</t>
         </is>
       </c>
-      <c r="C83" s="12" t="inlineStr">
+      <c r="C95" s="12" t="inlineStr">
         <is>
           <t>A reader could draw a false comparison</t>
         </is>
       </c>
-      <c r="D83" s="8" t="n"/>
-      <c r="E83" s="12" t="inlineStr">
+      <c r="D95" s="8" t="n"/>
+      <c r="E95" s="12" t="inlineStr">
         <is>
           <t>Fail — Blocking; do not publish that report</t>
         </is>
       </c>
-      <c r="F83" s="8" t="n"/>
-    </row>
-    <row r="84" ht="32" customHeight="1">
-      <c r="B84" s="21" t="inlineStr">
+      <c r="F95" s="8" t="n"/>
+    </row>
+    <row r="96" ht="32" customHeight="1">
+      <c r="B96" s="21" t="inlineStr">
         <is>
           <t>Remember.  Check tooltips and text boxes as carefully as charts. A single sentence in a text box is enough to fail this check.</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="8" customHeight="1"/>
-    <row r="86" ht="22" customHeight="1">
-      <c r="A86" s="5" t="inlineStr">
+    <row r="97" ht="8" customHeight="1"/>
+    <row r="98" ht="22" customHeight="1">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>6. RECORD THE RESULT</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="B87" s="13" t="inlineStr">
+    <row r="99" ht="20" customHeight="1">
+      <c r="B99" s="13" t="inlineStr">
         <is>
           <t>6.1 In document 22</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="16" t="n">
+    <row r="100" ht="16" customHeight="1">
+      <c r="A100" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B88" s="14" t="inlineStr">
+      <c r="B100" s="14" t="inlineStr">
         <is>
           <t>Open X:\retail-sector-health\docs\22_Validation_Results.xlsx in Excel.</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="16" t="n">
+    <row r="101" ht="16" customHeight="1">
+      <c r="A101" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B89" s="14" t="inlineStr">
+      <c r="B101" s="14" t="inlineStr">
         <is>
           <t>Select the Run Summary tab. Find the row for this run.</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="29" customHeight="1">
-      <c r="B90" s="17" t="inlineStr">
+    <row r="102" ht="29" customHeight="1">
+      <c r="B102" s="17" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C90" s="14" t="inlineStr">
+      <c r="C102" s="14" t="inlineStr">
         <is>
           <t>If you are checking during the first build, the run is Run 1. If Run 1 is not there yet, type Run 1 in the first empty Run ID cell.</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="29" customHeight="1">
-      <c r="B91" s="17" t="inlineStr">
+    <row r="103" ht="29" customHeight="1">
+      <c r="B103" s="17" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C91" s="14" t="inlineStr">
+      <c r="C103" s="14" t="inlineStr">
         <is>
           <t>Fill in Date, Trigger (choose from the drop-down: Initial build for the first build), Model / commit reference and Run by.</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="29" customHeight="1">
-      <c r="B92" s="17" t="inlineStr">
+    <row r="104" ht="29" customHeight="1">
+      <c r="B104" s="17" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C92" s="14" t="inlineStr">
+      <c r="C104" s="14" t="inlineStr">
         <is>
           <t>For Model / commit reference, open PowerShell, run the command below, and type the seven characters it prints.</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="16" customHeight="1">
-      <c r="B93" s="17" t="inlineStr">
+    <row r="105" ht="16" customHeight="1">
+      <c r="B105" s="17" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C93" s="14" t="inlineStr">
+      <c r="C105" s="14" t="inlineStr">
         <is>
           <t>Do not type in the columns from Checks recorded to Outcome. They are formulas and fill themselves in.</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="15" customHeight="1">
-      <c r="B94" s="22" t="inlineStr">
+    <row r="106" ht="15" customHeight="1">
+      <c r="B106" s="22" t="inlineStr">
         <is>
           <t>git -C X:\retail-sector-health log -1 --format=%h</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="6" customHeight="1"/>
-    <row r="96" ht="16" customHeight="1">
-      <c r="A96" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B96" s="14" t="inlineStr">
-        <is>
-          <t>Select the Check Results tab. Find the row whose Run ID is this run and whose # is 8.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="16" customHeight="1">
-      <c r="A97" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B97" s="14" t="inlineStr">
-        <is>
-          <t>Fill in four cells on that row:</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="16" customHeight="1">
-      <c r="B98" s="17" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C98" s="14" t="inlineStr">
-        <is>
-          <t>Result: choose Pass, Fail or N/A from the drop-down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="16" customHeight="1">
-      <c r="B99" s="17" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C99" s="14" t="inlineStr">
-        <is>
-          <t>Observed value / evidence: the numbers you saw — see the examples below. Never just ‘ok’.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="16" customHeight="1">
-      <c r="B100" s="17" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C100" s="14" t="inlineStr">
-        <is>
-          <t>Checked by: your name or initials.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="16" customHeight="1">
-      <c r="B101" s="17" t="inlineStr">
-        <is>
-          <t>◦</t>
-        </is>
-      </c>
-      <c r="C101" s="14" t="inlineStr">
-        <is>
-          <t>Date checked: today’s date.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="16" customHeight="1">
-      <c r="A102" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B102" s="14" t="inlineStr">
-        <is>
-          <t>Save the workbook. Go back to Run Summary: Checks recorded has gone up by one.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>Situation</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>Write this in Observed value / evidence</t>
-        </is>
-      </c>
-      <c r="D103" s="7" t="n"/>
-      <c r="E103" s="7" t="n"/>
-      <c r="F103" s="8" t="n"/>
-    </row>
-    <row r="104" ht="28" customHeight="1">
-      <c r="B104" s="10" t="inlineStr">
-        <is>
-          <t>Example of a pass</t>
-        </is>
-      </c>
-      <c r="C104" s="10" t="inlineStr">
-        <is>
-          <t>All 15 rows checked across R1–R3 · 3.5 uses National Liquor Stores Real YoY % · every Tier 3 axis titled Cases · no mixed tooltip or sentence</t>
-        </is>
-      </c>
-      <c r="D104" s="7" t="n"/>
-      <c r="E104" s="7" t="n"/>
-      <c r="F104" s="8" t="n"/>
-    </row>
-    <row r="105" ht="28" customHeight="1">
-      <c r="B105" s="12" t="inlineStr">
-        <is>
-          <t>Example of another result</t>
-        </is>
-      </c>
-      <c r="C105" s="12" t="inlineStr">
-        <is>
-          <t>Fail: 4.9 text says ‘volume grew faster than sales’ — compares cases with nominal dollars</t>
-        </is>
-      </c>
-      <c r="D105" s="7" t="n"/>
-      <c r="E105" s="7" t="n"/>
-      <c r="F105" s="8" t="n"/>
-    </row>
-    <row r="106" ht="16" customHeight="1">
-      <c r="B106" s="20" t="inlineStr">
-        <is>
-          <t>Examples show the wording and level of detail to aim for. The numbers in them are illustrations, not expected values.</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="20" customHeight="1">
-      <c r="B107" s="13" t="inlineStr">
-        <is>
-          <t>6.2 In document 26</t>
-        </is>
-      </c>
-    </row>
+    <row r="107" ht="6" customHeight="1"/>
     <row r="108" ht="16" customHeight="1">
       <c r="A108" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B108" s="14" t="inlineStr">
+        <is>
+          <t>Select the Check Results tab. Find the row whose Run ID is this run and whose # is 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="16" customHeight="1">
+      <c r="A109" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B109" s="14" t="inlineStr">
+        <is>
+          <t>Fill in four cells on that row:</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="16" customHeight="1">
+      <c r="B110" s="17" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C110" s="14" t="inlineStr">
+        <is>
+          <t>Result: choose Pass, Fail or N/A from the drop-down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="16" customHeight="1">
+      <c r="B111" s="17" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C111" s="14" t="inlineStr">
+        <is>
+          <t>Observed value / evidence: the numbers you saw — see the examples below. Never just ‘ok’.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="16" customHeight="1">
+      <c r="B112" s="17" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C112" s="14" t="inlineStr">
+        <is>
+          <t>Checked by: your name or initials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="16" customHeight="1">
+      <c r="B113" s="17" t="inlineStr">
+        <is>
+          <t>◦</t>
+        </is>
+      </c>
+      <c r="C113" s="14" t="inlineStr">
+        <is>
+          <t>Date checked: today’s date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="16" customHeight="1">
+      <c r="A114" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B114" s="14" t="inlineStr">
+        <is>
+          <t>Save the workbook. Go back to Run Summary: Checks recorded has gone up by one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="20" customHeight="1">
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>Situation</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>Write this in Observed value / evidence</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="n"/>
+      <c r="E115" s="7" t="n"/>
+      <c r="F115" s="8" t="n"/>
+    </row>
+    <row r="116" ht="29.5" customHeight="1">
+      <c r="B116" s="10" t="inlineStr">
+        <is>
+          <t>Example of a pass</t>
+        </is>
+      </c>
+      <c r="C116" s="10" t="inlineStr">
+        <is>
+          <t>All 27 rows checked across R1–R3 · 3.5 uses National Liquor Stores Real YoY % · every Tier 3 axis titled Cases · no mixed tooltip or sentence</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="n"/>
+      <c r="E116" s="7" t="n"/>
+      <c r="F116" s="8" t="n"/>
+    </row>
+    <row r="117" ht="28" customHeight="1">
+      <c r="B117" s="12" t="inlineStr">
+        <is>
+          <t>Example of another result</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>Fail: 4.9 text says ‘volume grew faster than sales’ — compares cases with nominal dollars</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="n"/>
+      <c r="E117" s="7" t="n"/>
+      <c r="F117" s="8" t="n"/>
+    </row>
+    <row r="118" ht="16" customHeight="1">
+      <c r="B118" s="20" t="inlineStr">
+        <is>
+          <t>Examples show the wording and level of detail to aim for. The numbers in them are illustrations, not expected values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="20" customHeight="1">
+      <c r="B119" s="13" t="inlineStr">
+        <is>
+          <t>6.2 In document 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="16" customHeight="1">
+      <c r="A120" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B108" s="14" t="inlineStr">
+      <c r="B120" s="14" t="inlineStr">
         <is>
           <t>Open X:\retail-sector-health\docs\26_Validation_Timing_Checklist.xlsx and select the Build Checklist tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="29" customHeight="1">
-      <c r="A109" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B109" s="14" t="inlineStr">
-        <is>
-          <t>Find the row with the Ref shown below that matches where you are in the build. Set Result to the same result, and fill Date, Checked by and Observed value the same way.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="20" customHeight="1">
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>Ref in doc 26</t>
-        </is>
-      </c>
-      <c r="C110" s="6" t="inlineStr">
-        <is>
-          <t>When it applies</t>
-        </is>
-      </c>
-      <c r="D110" s="7" t="n"/>
-      <c r="E110" s="7" t="n"/>
-      <c r="F110" s="8" t="n"/>
-    </row>
-    <row r="111" ht="28" customHeight="1">
-      <c r="B111" s="10" t="inlineStr">
-        <is>
-          <t>G7.04, G7.06, G7.07, G7.10, G7.12, G7.13</t>
-        </is>
-      </c>
-      <c r="C111" s="10" t="inlineStr">
-        <is>
-          <t>The page carrying the visual is finished</t>
-        </is>
-      </c>
-      <c r="D111" s="7" t="n"/>
-      <c r="E111" s="7" t="n"/>
-      <c r="F111" s="8" t="n"/>
-    </row>
-    <row r="112" ht="16" customHeight="1">
-      <c r="B112" s="12" t="inlineStr">
-        <is>
-          <t>G8.01, G8.03, G8.05</t>
-        </is>
-      </c>
-      <c r="C112" s="12" t="inlineStr">
-        <is>
-          <t>The R1, R2 and R3 report passes</t>
-        </is>
-      </c>
-      <c r="D112" s="7" t="n"/>
-      <c r="E112" s="7" t="n"/>
-      <c r="F112" s="8" t="n"/>
-    </row>
-    <row r="113" ht="8" customHeight="1"/>
-    <row r="114" ht="22" customHeight="1">
-      <c r="A114" s="5" t="inlineStr">
-        <is>
-          <t>7. IF IT FAILS</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="20" customHeight="1">
-      <c r="B115" s="13" t="inlineStr">
-        <is>
-          <t>7.1 What usually causes it</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="20" customHeight="1">
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>What you see</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>Likely cause</t>
-        </is>
-      </c>
-      <c r="D116" s="8" t="n"/>
-      <c r="E116" s="6" t="inlineStr">
-        <is>
-          <t>What to do</t>
-        </is>
-      </c>
-      <c r="F116" s="8" t="n"/>
-    </row>
-    <row r="117" ht="28" customHeight="1">
-      <c r="B117" s="10" t="inlineStr">
-        <is>
-          <t>Nominal measure on 3.5</t>
-        </is>
-      </c>
-      <c r="C117" s="10" t="inlineStr">
-        <is>
-          <t>National Liquor Stores Nominal YoY % used instead of Real</t>
-        </is>
-      </c>
-      <c r="D117" s="8" t="n"/>
-      <c r="E117" s="10" t="inlineStr">
-        <is>
-          <t>Replace it with National Liquor Stores Real YoY %</t>
-        </is>
-      </c>
-      <c r="F117" s="8" t="n"/>
-    </row>
-    <row r="118" ht="28" customHeight="1">
-      <c r="B118" s="12" t="inlineStr">
-        <is>
-          <t>Axis not titled Cases</t>
-        </is>
-      </c>
-      <c r="C118" s="12" t="inlineStr">
-        <is>
-          <t>Default axis title</t>
-        </is>
-      </c>
-      <c r="D118" s="8" t="n"/>
-      <c r="E118" s="12" t="inlineStr">
-        <is>
-          <t>Format visual → Y-axis → Title → type a title containing Cases</t>
-        </is>
-      </c>
-      <c r="F118" s="8" t="n"/>
-    </row>
-    <row r="119" ht="28" customHeight="1">
-      <c r="B119" s="10" t="inlineStr">
-        <is>
-          <t>Sentence compares cases and dollars</t>
-        </is>
-      </c>
-      <c r="C119" s="10" t="inlineStr">
-        <is>
-          <t>Wording</t>
-        </is>
-      </c>
-      <c r="D119" s="8" t="n"/>
-      <c r="E119" s="10" t="inlineStr">
-        <is>
-          <t>Rewrite to compare growth in cases with real growth, or remove</t>
-        </is>
-      </c>
-      <c r="F119" s="8" t="n"/>
-    </row>
-    <row r="120" ht="20" customHeight="1">
-      <c r="B120" s="13" t="inlineStr">
-        <is>
-          <t>7.2 Record the failure</t>
         </is>
       </c>
     </row>
     <row r="121" ht="29" customHeight="1">
       <c r="A121" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B121" s="14" t="inlineStr">
+        <is>
+          <t>Find the row with the Ref shown below that matches where you are in the build. Set Result to the same result, and fill Date, Checked by and Observed value the same way.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="20" customHeight="1">
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>Ref in doc 26</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>When it applies</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="n"/>
+      <c r="E122" s="7" t="n"/>
+      <c r="F122" s="8" t="n"/>
+    </row>
+    <row r="123" ht="70" customHeight="1">
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>G7.04, G7.06, G7.07, G7.10, G7.11, G7.12, G7.13, and G7.14 to G7.16 for the drillthrough and tooltip pages</t>
+        </is>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
+          <t>The page carrying the visual is finished</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="n"/>
+      <c r="E123" s="7" t="n"/>
+      <c r="F123" s="8" t="n"/>
+    </row>
+    <row r="124" ht="16" customHeight="1">
+      <c r="B124" s="12" t="inlineStr">
+        <is>
+          <t>G8.01, G8.03, G8.05</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>The R1, R2 and R3 report passes</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="n"/>
+      <c r="E124" s="7" t="n"/>
+      <c r="F124" s="8" t="n"/>
+    </row>
+    <row r="125" ht="8" customHeight="1"/>
+    <row r="126" ht="22" customHeight="1">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>7. IF IT FAILS</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="20" customHeight="1">
+      <c r="B127" s="13" t="inlineStr">
+        <is>
+          <t>7.1 What usually causes it</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1">
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>What you see</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>Likely cause</t>
+        </is>
+      </c>
+      <c r="D128" s="8" t="n"/>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>What to do</t>
+        </is>
+      </c>
+      <c r="F128" s="8" t="n"/>
+    </row>
+    <row r="129" ht="28" customHeight="1">
+      <c r="B129" s="10" t="inlineStr">
+        <is>
+          <t>Nominal measure on 3.5</t>
+        </is>
+      </c>
+      <c r="C129" s="10" t="inlineStr">
+        <is>
+          <t>National Liquor Stores Nominal YoY % used instead of Real</t>
+        </is>
+      </c>
+      <c r="D129" s="8" t="n"/>
+      <c r="E129" s="10" t="inlineStr">
+        <is>
+          <t>Replace it with National Liquor Stores Real YoY %</t>
+        </is>
+      </c>
+      <c r="F129" s="8" t="n"/>
+    </row>
+    <row r="130" ht="28" customHeight="1">
+      <c r="B130" s="12" t="inlineStr">
+        <is>
+          <t>Axis not titled Cases</t>
+        </is>
+      </c>
+      <c r="C130" s="12" t="inlineStr">
+        <is>
+          <t>Default axis title</t>
+        </is>
+      </c>
+      <c r="D130" s="8" t="n"/>
+      <c r="E130" s="12" t="inlineStr">
+        <is>
+          <t>Format visual → Y-axis → Title → type a title containing Cases</t>
+        </is>
+      </c>
+      <c r="F130" s="8" t="n"/>
+    </row>
+    <row r="131" ht="28" customHeight="1">
+      <c r="B131" s="10" t="inlineStr">
+        <is>
+          <t>Sentence compares cases and dollars</t>
+        </is>
+      </c>
+      <c r="C131" s="10" t="inlineStr">
+        <is>
+          <t>Wording</t>
+        </is>
+      </c>
+      <c r="D131" s="8" t="n"/>
+      <c r="E131" s="10" t="inlineStr">
+        <is>
+          <t>Rewrite to compare growth in cases with real growth, or remove</t>
+        </is>
+      </c>
+      <c r="F131" s="8" t="n"/>
+    </row>
+    <row r="132" ht="20" customHeight="1">
+      <c r="B132" s="13" t="inlineStr">
+        <is>
+          <t>7.2 Record the failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="29" customHeight="1">
+      <c r="A133" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B121" s="14" t="inlineStr">
+      <c r="B133" s="14" t="inlineStr">
         <is>
           <t>On the Check Results tab of document 22, set Result to Fail for check 8. Write the numbers you saw in Observed value. Do not change it to N/A and do not clear it.</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="16" customHeight="1">
-      <c r="A122" s="16" t="n">
+    <row r="134" ht="16" customHeight="1">
+      <c r="A134" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B122" s="14" t="inlineStr">
+      <c r="B134" s="14" t="inlineStr">
         <is>
           <t>Select the Failure Log tab and fill the first empty row:</t>
         </is>
       </c>
     </row>
-    <row r="123" ht="16" customHeight="1">
-      <c r="B123" s="17" t="inlineStr">
+    <row r="135" ht="16" customHeight="1">
+      <c r="B135" s="17" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C123" s="14" t="inlineStr">
+      <c r="C135" s="14" t="inlineStr">
         <is>
           <t>Failure ID: the next number — F-001, then F-002 and so on.</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="16" customHeight="1">
-      <c r="B124" s="17" t="inlineStr">
+    <row r="136" ht="16" customHeight="1">
+      <c r="B136" s="17" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C124" s="14" t="inlineStr">
+      <c r="C136" s="14" t="inlineStr">
         <is>
           <t>Run ID and Check #: this run and check number.</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="16" customHeight="1">
-      <c r="B125" s="17" t="inlineStr">
+    <row r="137" ht="16" customHeight="1">
+      <c r="B137" s="17" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C125" s="14" t="inlineStr">
+      <c r="C137" s="14" t="inlineStr">
         <is>
           <t>What was observed: the same numbers.</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="16" customHeight="1">
-      <c r="B126" s="17" t="inlineStr">
+    <row r="138" ht="16" customHeight="1">
+      <c r="B138" s="17" t="inlineStr">
         <is>
           <t>◦</t>
         </is>
       </c>
-      <c r="C126" s="14" t="inlineStr">
+      <c r="C138" s="14" t="inlineStr">
         <is>
           <t>Root cause: what you found, or ‘not yet known’.</t>
         </is>
       </c>
     </row>
-    <row r="127" ht="16" customHeight="1">
-      <c r="A127" s="16" t="n">
+    <row r="139" ht="16" customHeight="1">
+      <c r="A139" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B127" s="14" t="inlineStr">
+      <c r="B139" s="14" t="inlineStr">
         <is>
           <t>Fix the cause. Then fill Fix applied, Fixed by and Date fixed. Status changes by itself to ‘Fix applied — not re-verified’.</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="29" customHeight="1">
-      <c r="A128" s="16" t="n">
+    <row r="140" ht="29" customHeight="1">
+      <c r="A140" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B128" s="14" t="inlineStr">
+      <c r="B140" s="14" t="inlineStr">
         <is>
           <t>Run the whole procedure again as a new run — on Run Summary add Run 2 with Trigger Ad hoc and name the fix in Notes. Record the new result against Run 2.</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="16" customHeight="1">
-      <c r="A129" s="16" t="n">
+    <row r="141" ht="16" customHeight="1">
+      <c r="A141" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B129" s="14" t="inlineStr">
+      <c r="B141" s="14" t="inlineStr">
         <is>
           <t>When it passes, type Run 2 in Re-verified in run on the Failure Log. Status changes to ‘Closed — re-verified’.</t>
         </is>
       </c>
     </row>
-    <row r="130" ht="8" customHeight="1"/>
-    <row r="131" ht="22" customHeight="1">
-      <c r="A131" s="5" t="inlineStr">
+    <row r="142" ht="8" customHeight="1"/>
+    <row r="143" ht="22" customHeight="1">
+      <c r="A143" s="5" t="inlineStr">
         <is>
           <t>8. WHEN TO RUN IT AGAIN</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="16" customHeight="1">
-      <c r="A132" s="15" t="inlineStr">
+    <row r="144" ht="16" customHeight="1">
+      <c r="A144" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B132" s="14" t="inlineStr">
+      <c r="B144" s="14" t="inlineStr">
         <is>
           <t>After any report visual or text is added or changed.</t>
         </is>
       </c>
     </row>
-    <row r="133" ht="16" customHeight="1">
-      <c r="A133" s="15" t="inlineStr">
+    <row r="145" ht="16" customHeight="1">
+      <c r="A145" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B133" s="14" t="inlineStr">
+      <c r="B145" s="14" t="inlineStr">
         <is>
           <t>At every report pass.</t>
         </is>
       </c>
     </row>
-    <row r="134" ht="8" customHeight="1"/>
-    <row r="135" ht="22" customHeight="1">
-      <c r="A135" s="5" t="inlineStr">
+    <row r="146" ht="8" customHeight="1"/>
+    <row r="147" ht="22" customHeight="1">
+      <c r="A147" s="5" t="inlineStr">
         <is>
           <t>9. REFERENCES</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="16" customHeight="1">
-      <c r="A136" s="15" t="inlineStr">
+    <row r="148" ht="16" customHeight="1">
+      <c r="A148" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B136" s="14" t="inlineStr">
+      <c r="B148" s="14" t="inlineStr">
         <is>
           <t>Document 02 §9 — the seventeen checks and their pass criteria.</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="16" customHeight="1">
-      <c r="A137" s="15" t="inlineStr">
+    <row r="149" ht="16" customHeight="1">
+      <c r="A149" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B137" s="14" t="inlineStr">
+      <c r="B149" s="14" t="inlineStr">
         <is>
           <t>Document 22, Check Catalog tab — what this check protects against and where it runs.</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="16" customHeight="1">
-      <c r="A138" s="15" t="inlineStr">
+    <row r="150" ht="16" customHeight="1">
+      <c r="A150" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B138" s="14" t="inlineStr">
+      <c r="B150" s="14" t="inlineStr">
         <is>
           <t>Document 25 — when each check is run, and when to re-run it.</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="16" customHeight="1">
-      <c r="A139" s="15" t="inlineStr">
+    <row r="151" ht="16" customHeight="1">
+      <c r="A151" s="15" t="inlineStr">
         <is>
           <t>•</t>
         </is>
       </c>
-      <c r="B139" s="14" t="inlineStr">
+      <c r="B151" s="14" t="inlineStr">
         <is>
           <t>Document 26 — the gate rows this check is ticked against.</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="8" customHeight="1"/>
-    <row r="141" ht="22" customHeight="1">
-      <c r="A141" s="5" t="inlineStr">
+    <row r="152" ht="8" customHeight="1"/>
+    <row r="153" ht="22" customHeight="1">
+      <c r="A153" s="5" t="inlineStr">
         <is>
           <t>10. AI ASSISTANCE DISCLOSURE</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="29" customHeight="1">
-      <c r="B142" s="14" t="inlineStr">
+    <row r="154" ht="29" customHeight="1">
+      <c r="B154" s="14" t="inlineStr">
         <is>
           <t>Portions of this procedure were drafted with the assistance of a generative AI system. The author defined the project and its validation approach and reviewed all content before publication.</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="43.5" customHeight="1">
-      <c r="B143" s="14" t="inlineStr">
+    <row r="155" ht="43.5" customHeight="1">
+      <c r="B155" s="14" t="inlineStr">
         <is>
           <t>The pass criterion is quoted from document 02 §9. Queries use only tables, columns and measures defined in documents 02 and 20, and the visual numbers come from the document 15 specification tables. Tool steps were checked against Microsoft Learn; where a screen label varies by version, the procedure says so.</t>
         </is>
@@ -2404,131 +2680,131 @@
     </row>
   </sheetData>
   <mergeCells count="123">
+    <mergeCell ref="B106:F106"/>
     <mergeCell ref="C52:F52"/>
-    <mergeCell ref="B106:F106"/>
-    <mergeCell ref="B129:F129"/>
     <mergeCell ref="B16:F16"/>
-    <mergeCell ref="C116:D116"/>
-    <mergeCell ref="B122:F122"/>
-    <mergeCell ref="C125:F125"/>
+    <mergeCell ref="C122:F122"/>
+    <mergeCell ref="E129:F129"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A86:F86"/>
     <mergeCell ref="C13:F13"/>
+    <mergeCell ref="E131:F131"/>
+    <mergeCell ref="C136:F136"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="A32:F32"/>
+    <mergeCell ref="E128:F128"/>
     <mergeCell ref="B60:F60"/>
+    <mergeCell ref="C93:D93"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C116:F116"/>
     <mergeCell ref="A38:F38"/>
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="B108:F108"/>
-    <mergeCell ref="C119:D119"/>
-    <mergeCell ref="E119:F119"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B92:F92"/>
     <mergeCell ref="C10:F10"/>
-    <mergeCell ref="B84:F84"/>
-    <mergeCell ref="E116:F116"/>
-    <mergeCell ref="C93:F93"/>
     <mergeCell ref="C50:F50"/>
-    <mergeCell ref="B143:F143"/>
     <mergeCell ref="C56:F56"/>
+    <mergeCell ref="C105:F105"/>
     <mergeCell ref="B20:F20"/>
-    <mergeCell ref="C105:F105"/>
     <mergeCell ref="B133:F133"/>
-    <mergeCell ref="B142:F142"/>
-    <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B94:F94"/>
+    <mergeCell ref="E93:F93"/>
     <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C83:D83"/>
-    <mergeCell ref="E117:F117"/>
+    <mergeCell ref="B144:F144"/>
     <mergeCell ref="B54:F54"/>
+    <mergeCell ref="C135:F135"/>
+    <mergeCell ref="B134:F134"/>
     <mergeCell ref="B121:F121"/>
+    <mergeCell ref="C28:F28"/>
     <mergeCell ref="B96:F96"/>
-    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="A2:F2"/>
     <mergeCell ref="C111:F111"/>
-    <mergeCell ref="A2:F2"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B120:F120"/>
-    <mergeCell ref="C92:F92"/>
-    <mergeCell ref="A141:F141"/>
     <mergeCell ref="C30:F30"/>
-    <mergeCell ref="A135:F135"/>
-    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="A126:F126"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="C14:F14"/>
-    <mergeCell ref="B88:F88"/>
-    <mergeCell ref="C98:F98"/>
-    <mergeCell ref="A114:F114"/>
+    <mergeCell ref="B148:F148"/>
+    <mergeCell ref="B99:F99"/>
+    <mergeCell ref="C137:F137"/>
     <mergeCell ref="C124:F124"/>
-    <mergeCell ref="C82:D82"/>
-    <mergeCell ref="A79:F79"/>
-    <mergeCell ref="C90:F90"/>
+    <mergeCell ref="A98:F98"/>
+    <mergeCell ref="A153:F153"/>
     <mergeCell ref="C123:F123"/>
+    <mergeCell ref="C138:F138"/>
+    <mergeCell ref="E130:F130"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B109:F109"/>
+    <mergeCell ref="C8:F8"/>
     <mergeCell ref="C110:F110"/>
-    <mergeCell ref="B109:F109"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C91:F91"/>
+    <mergeCell ref="B141:F141"/>
     <mergeCell ref="B59:F59"/>
-    <mergeCell ref="E83:F83"/>
+    <mergeCell ref="B150:F150"/>
     <mergeCell ref="C57:F57"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="C102:F102"/>
     <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B136:F136"/>
-    <mergeCell ref="A131:F131"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="E94:F94"/>
+    <mergeCell ref="B145:F145"/>
     <mergeCell ref="C58:F58"/>
-    <mergeCell ref="E118:F118"/>
+    <mergeCell ref="C129:D129"/>
     <mergeCell ref="C45:F45"/>
-    <mergeCell ref="B87:F87"/>
     <mergeCell ref="A19:F19"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="E95:F95"/>
+    <mergeCell ref="C113:F113"/>
     <mergeCell ref="C29:F29"/>
-    <mergeCell ref="B128:F128"/>
-    <mergeCell ref="C100:F100"/>
     <mergeCell ref="C112:F112"/>
-    <mergeCell ref="B137:F137"/>
+    <mergeCell ref="A143:F143"/>
     <mergeCell ref="C44:F44"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="B139:F139"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C131:D131"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="C12:F12"/>
-    <mergeCell ref="E81:F81"/>
     <mergeCell ref="C46:F46"/>
-    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="B154:F154"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="C51:F51"/>
-    <mergeCell ref="B138:F138"/>
     <mergeCell ref="C48:F48"/>
     <mergeCell ref="C23:F23"/>
+    <mergeCell ref="B100:F100"/>
     <mergeCell ref="C7:F7"/>
-    <mergeCell ref="B115:F115"/>
-    <mergeCell ref="B102:F102"/>
-    <mergeCell ref="E82:F82"/>
-    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B155:F155"/>
+    <mergeCell ref="B149:F149"/>
     <mergeCell ref="C49:F49"/>
-    <mergeCell ref="C101:F101"/>
-    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="B151:F151"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A91:F91"/>
     <mergeCell ref="C104:F104"/>
     <mergeCell ref="B132:F132"/>
-    <mergeCell ref="C118:D118"/>
-    <mergeCell ref="C126:F126"/>
+    <mergeCell ref="A147:F147"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="C130:D130"/>
     <mergeCell ref="C25:F25"/>
+    <mergeCell ref="B140:F140"/>
     <mergeCell ref="C103:F103"/>
+    <mergeCell ref="B40:F40"/>
     <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="C99:F99"/>
+    <mergeCell ref="C117:F117"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B33:F33"/>
-    <mergeCell ref="C81:D81"/>
     <mergeCell ref="B89:F89"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C115:F115"/>
     <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B97:F97"/>
     <mergeCell ref="B35:F35"/>
   </mergeCells>
-  <conditionalFormatting sqref="F62:F76">
+  <conditionalFormatting sqref="F62:F84">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Pass"</formula>
     </cfRule>
@@ -2537,7 +2813,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F62:F76" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F62:F88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pass,Fail,N/A"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/validation/V08_Cases_vs_Dollars_Separation.xlsx
+++ b/docs/validation/V08_Cases_vs_Dollars_Separation.xlsx
@@ -1983,7 +1983,7 @@
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>Narratives on R1 Pages 1–2 (1.8) and R3 (10.8)</t>
+          <t>Narratives on R1 Page 1 (1.8) and R3 Page 4 (10.8)</t>
         </is>
       </c>
       <c r="E88" s="10" t="inlineStr">
@@ -2345,7 +2345,7 @@
     <row r="123" ht="70" customHeight="1">
       <c r="B123" s="10" t="inlineStr">
         <is>
-          <t>G7.04, G7.06, G7.07, G7.10, G7.11, G7.12, G7.13, and G7.14 to G7.16 for the drillthrough and tooltip pages</t>
+          <t>G7.04, G7.06, G7.07, G7.10, G7.11, G7.12, G7.13, and G7.14 and G7.15 for the drillthrough and tooltip pages</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
@@ -2702,13 +2702,13 @@
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="B108:F108"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C50:F50"/>
     <mergeCell ref="B118:F118"/>
     <mergeCell ref="B92:F92"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C50:F50"/>
     <mergeCell ref="C56:F56"/>
+    <mergeCell ref="B20:F20"/>
     <mergeCell ref="C105:F105"/>
-    <mergeCell ref="B20:F20"/>
     <mergeCell ref="B133:F133"/>
     <mergeCell ref="E93:F93"/>
     <mergeCell ref="C27:F27"/>
@@ -2717,14 +2717,14 @@
     <mergeCell ref="C135:F135"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B121:F121"/>
+    <mergeCell ref="B96:F96"/>
     <mergeCell ref="C28:F28"/>
-    <mergeCell ref="B96:F96"/>
+    <mergeCell ref="C111:F111"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="C111:F111"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B120:F120"/>
+    <mergeCell ref="A126:F126"/>
     <mergeCell ref="C30:F30"/>
-    <mergeCell ref="A126:F126"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="B148:F148"/>
@@ -2735,11 +2735,11 @@
     <mergeCell ref="A153:F153"/>
     <mergeCell ref="C123:F123"/>
     <mergeCell ref="C138:F138"/>
+    <mergeCell ref="C110:F110"/>
+    <mergeCell ref="B109:F109"/>
     <mergeCell ref="E130:F130"/>
     <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B109:F109"/>
     <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C110:F110"/>
     <mergeCell ref="B141:F141"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B150:F150"/>
@@ -2755,20 +2755,20 @@
     <mergeCell ref="C45:F45"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="C95:D95"/>
+    <mergeCell ref="C113:F113"/>
     <mergeCell ref="E95:F95"/>
-    <mergeCell ref="C113:F113"/>
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="C112:F112"/>
     <mergeCell ref="A143:F143"/>
     <mergeCell ref="C44:F44"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="B139:F139"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C46:F46"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="C131:D131"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C46:F46"/>
     <mergeCell ref="B154:F154"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="C51:F51"/>
@@ -2776,31 +2776,31 @@
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="B100:F100"/>
     <mergeCell ref="C7:F7"/>
+    <mergeCell ref="B140:F140"/>
     <mergeCell ref="B155:F155"/>
     <mergeCell ref="B149:F149"/>
     <mergeCell ref="C49:F49"/>
     <mergeCell ref="B151:F151"/>
     <mergeCell ref="B101:F101"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A91:F91"/>
     <mergeCell ref="C104:F104"/>
     <mergeCell ref="B132:F132"/>
+    <mergeCell ref="A91:F91"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="B119:F119"/>
     <mergeCell ref="C130:D130"/>
     <mergeCell ref="C25:F25"/>
-    <mergeCell ref="B140:F140"/>
     <mergeCell ref="C103:F103"/>
+    <mergeCell ref="C117:F117"/>
+    <mergeCell ref="B127:F127"/>
     <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="C117:F117"/>
     <mergeCell ref="C9:F9"/>
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="B89:F89"/>
     <mergeCell ref="A6:F6"/>
+    <mergeCell ref="C115:F115"/>
     <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C115:F115"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B35:F35"/>
   </mergeCells>
@@ -2814,7 +2814,7 @@
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="F62:F88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Pass,Fail,N/A"</formula1>
+      <formula1>"Pass,Fail,N/A,Not run"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
